--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
   <si>
     <t>Mat</t>
   </si>
@@ -68,24 +68,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>NAZARIO</t>
-  </si>
-  <si>
-    <t>KEVIN ISAAC</t>
-  </si>
-  <si>
-    <t>EDGAR</t>
   </si>
 </sst>
 </file>
@@ -577,16 +559,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -600,16 +585,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>75</v>
+      </c>
+      <c r="H3">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -665,16 +653,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>84.20999999999999</v>
+        <v>81.58</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -691,16 +679,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>71.88</v>
+        <v>75</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -710,7 +698,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -740,52 +728,6 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920005</v>
-      </c>
-      <c r="B2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>20330051920018</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -68,6 +68,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>IXMATLAHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LIZBETH JOSELYN</t>
   </si>
 </sst>
 </file>
@@ -698,7 +707,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -728,6 +737,29 @@
         <v>16</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920235</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -73,10 +73,19 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
     <t>LIZBETH JOSELYN</t>
+  </si>
+  <si>
+    <t>YAEL</t>
   </si>
 </sst>
 </file>
@@ -688,13 +697,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>75</v>
+        <v>90.63</v>
       </c>
       <c r="H3">
         <v>7.1</v>
@@ -707,7 +716,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -745,10 +754,10 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -757,6 +766,29 @@
         <v>9</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
+++ b/docentes/Barañon Samaniego Graciela de los Ángeles - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -70,19 +70,10 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
   </si>
   <si>
     <t>YAEL</t>
@@ -716,7 +707,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -748,16 +739,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920235</v>
+        <v>21330051920222</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -766,29 +757,6 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920222</v>
-      </c>
-      <c r="B3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>
